--- a/xiuxian配置表/indir/技能表.xlsx
+++ b/xiuxian配置表/indir/技能表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="285" yWindow="735" windowWidth="24300" windowHeight="11025" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="2010" windowWidth="27330" windowHeight="12705" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_zhandou_passive" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_zhandou_active" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_general_passive" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_buff" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="战斗effects效果介绍" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="z_zhandou_active" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="z_zhandou_passive" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="z_general_passive" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="z_buff" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="战斗effects效果介绍" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -71,8 +71,42 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Noto Sans SC"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF364152"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF364152"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="9.9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -94,8 +128,14 @@
         <fgColor rgb="FFF7FAF5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -143,12 +183,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -175,24 +230,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,6 +282,54 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -613,532 +698,1873 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="16.25" customWidth="1" style="17" min="1" max="1"/>
-    <col width="18.75" customWidth="1" style="17" min="2" max="6"/>
-    <col width="32.5" customWidth="1" style="17" min="7" max="7"/>
-    <col width="18.75" customWidth="1" style="17" min="8" max="9"/>
-    <col width="32.5" customWidth="1" style="17" min="10" max="10"/>
-    <col width="18.75" customWidth="1" style="17" min="11" max="11"/>
-    <col width="9" customWidth="1" style="17" min="12" max="16384"/>
+    <col width="35.875" bestFit="1" customWidth="1" style="11" min="1" max="1"/>
+    <col width="11.625" bestFit="1" customWidth="1" style="11" min="2" max="2"/>
+    <col width="18.75" customWidth="1" style="11" min="3" max="3"/>
+    <col width="5.25" bestFit="1" customWidth="1" style="11" min="4" max="4"/>
+    <col width="7.25" bestFit="1" customWidth="1" style="11" min="5" max="5"/>
+    <col width="10.375" bestFit="1" customWidth="1" style="11" min="6" max="6"/>
+    <col width="32.5" customWidth="1" style="11" min="7" max="7"/>
+    <col width="15.25" customWidth="1" style="11" min="8" max="8"/>
+    <col width="18.75" customWidth="1" style="11" min="9" max="9"/>
+    <col width="7" bestFit="1" customWidth="1" style="11" min="10" max="10"/>
+    <col width="9.75" bestFit="1" customWidth="1" style="11" min="11" max="11"/>
+    <col width="9.875" bestFit="1" customWidth="1" style="11" min="12" max="12"/>
+    <col width="10" bestFit="1" customWidth="1" style="11" min="13" max="13"/>
+    <col width="14.75" bestFit="1" customWidth="1" style="11" min="14" max="14"/>
+    <col width="11.25" bestFit="1" customWidth="1" style="11" min="15" max="15"/>
+    <col width="10.125" bestFit="1" customWidth="1" style="11" min="16" max="16"/>
+    <col width="12.875" bestFit="1" customWidth="1" style="11" min="17" max="17"/>
+    <col width="128.75" bestFit="1" customWidth="1" style="11" min="18" max="18"/>
+    <col width="32.5" customWidth="1" style="11" min="19" max="19"/>
+    <col width="9" customWidth="1" style="11" min="20" max="20"/>
+    <col width="9" customWidth="1" style="11" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>键</t>
-        </is>
-      </c>
-      <c r="B1" s="30" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="30" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="31" t="inlineStr">
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>阶位</t>
         </is>
       </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="E1" s="35" t="inlineStr">
         <is>
           <t>品质</t>
         </is>
       </c>
-      <c r="F1" s="30" t="inlineStr">
-        <is>
-          <t>图标</t>
-        </is>
-      </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>tag</t>
+      <c r="F1" s="36" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="G1" s="31" t="inlineStr">
+        <is>
+          <t>标签</t>
         </is>
       </c>
       <c r="H1" s="31" t="inlineStr">
         <is>
-          <t>cd</t>
-        </is>
-      </c>
-      <c r="I1" s="30" t="inlineStr">
-        <is>
-          <t>runtype</t>
-        </is>
-      </c>
-      <c r="J1" s="30" t="inlineStr">
+          <t>vfx_preset</t>
+        </is>
+      </c>
+      <c r="I1" s="31" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="J1" s="31" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="K1" s="31" t="inlineStr">
+        <is>
+          <t>targetarg</t>
+        </is>
+      </c>
+      <c r="L1" s="37" t="inlineStr">
+        <is>
+          <t>cast_time</t>
+        </is>
+      </c>
+      <c r="M1" s="35" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
+      <c r="N1" s="31" t="inlineStr">
+        <is>
+          <t>cost_resource</t>
+        </is>
+      </c>
+      <c r="O1" s="35" t="inlineStr">
+        <is>
+          <t>cost_value</t>
+        </is>
+      </c>
+      <c r="P1" s="31" t="inlineStr">
+        <is>
+          <t>activation</t>
+        </is>
+      </c>
+      <c r="Q1" s="35" t="inlineStr">
+        <is>
+          <t>power_scale</t>
+        </is>
+      </c>
+      <c r="R1" s="31" t="inlineStr">
         <is>
           <t>效果</t>
         </is>
       </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D2" s="38" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="38" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="F2" s="27" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="G2" s="27" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="H2" s="28" t="inlineStr">
-        <is>
-          <t>cd</t>
-        </is>
-      </c>
-      <c r="I2" s="27" t="inlineStr">
-        <is>
-          <t>runtype</t>
-        </is>
-      </c>
-      <c r="J2" s="27" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
+        <is>
+          <t>req_realm</t>
+        </is>
+      </c>
+      <c r="G2" s="32" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H2" s="32" t="inlineStr">
+        <is>
+          <t>vfx_preset</t>
+        </is>
+      </c>
+      <c r="I2" s="32" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J2" s="32" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="K2" s="32" t="inlineStr">
+        <is>
+          <t>targetarg</t>
+        </is>
+      </c>
+      <c r="L2" s="39" t="inlineStr">
+        <is>
+          <t>cast_time</t>
+        </is>
+      </c>
+      <c r="M2" s="38" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
+      <c r="N2" s="32" t="inlineStr">
+        <is>
+          <t>cost_resource</t>
+        </is>
+      </c>
+      <c r="O2" s="38" t="inlineStr">
+        <is>
+          <t>cost_value</t>
+        </is>
+      </c>
+      <c r="P2" s="32" t="inlineStr">
+        <is>
+          <t>activation</t>
+        </is>
+      </c>
+      <c r="Q2" s="38" t="inlineStr">
+        <is>
+          <t>power_scale</t>
+        </is>
+      </c>
+      <c r="R2" s="32" t="inlineStr">
         <is>
           <t>effects</t>
         </is>
       </c>
-      <c r="K2" s="27" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="40" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="40" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L3" s="41" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M3" s="40" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O3" s="40" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P3" s="33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q3" s="40" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R3" s="33" t="inlineStr">
         <is>
           <t>json</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J3" s="24" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>k1</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="24" t="n"/>
-      <c r="J4" s="24" t="n"/>
-      <c r="K4" s="24" t="n"/>
-    </row>
-    <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0001</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0001</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>铁骨</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="n">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="40" t="n"/>
+      <c r="E4" s="40" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="41" t="n"/>
+      <c r="M4" s="40" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="40" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="40" t="n"/>
+      <c r="R4" s="33" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="33" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="40" t="n"/>
+      <c r="E5" s="40" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="41" t="n"/>
+      <c r="M5" s="40" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="40" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="40" t="n"/>
+      <c r="R5" s="33" t="n"/>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.qi_bolt</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>火球术</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>lianqi</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>attack, spell, ranged, filler</t>
+        </is>
+      </c>
+      <c r="H6" s="33" t="inlineStr">
+        <is>
+          <t>qi_bolt_projectile</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>低耗灵力弹，适合新手稳定补伤害。</t>
+        </is>
+      </c>
+      <c r="J6" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L6" s="41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O6" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="33" t="inlineStr">
+        <is>
+          <t>[["damage", "40"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.wind_step</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>法力护盾</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>lianqi</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>mobility, shield, defense</t>
+        </is>
+      </c>
+      <c r="H7" s="33" t="n"/>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>短暂借风护身，提升出手速度并获得灵力护盾。</t>
+        </is>
+      </c>
+      <c r="J7" s="33" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="K7" s="33" t="n"/>
+      <c r="L7" s="41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O7" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="33" t="inlineStr">
+        <is>
+          <t>["shield","40"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.sword_qi</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>破空剑气</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>lianqi</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>attack, sword, ranged, execute</t>
+        </is>
+      </c>
+      <c r="H8" s="33" t="inlineStr">
+        <is>
+          <t>sword_qi_projectile</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>集中剑气斩向虚弱敌人，负责收割和压低战斗时长。</t>
+        </is>
+      </c>
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K8" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L8" s="41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O8" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="33" t="inlineStr">
+        <is>
+          <t>[["buff", "buff_0008"], ["buff", "buff_0009"], ["buff", "buff_0010"], ["buff", "buff_0011"], ["buff", "buff_0012"], ["buff", "buff_0013"], ["buff", "buff_0014"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.blood_strike</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>震血拳</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>zhuji</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>attack, body, melee, control</t>
+        </is>
+      </c>
+      <c r="H9" s="33" t="n"/>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>震血拳</t>
+        </is>
+      </c>
+      <c r="J9" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L9" s="41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M9" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" s="33" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+      <c r="O9" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="P9" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>beattack</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t>[["attrschange","castspd","20"]]</t>
-        </is>
-      </c>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>被攻击前增加20出手速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0002</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0002</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>剑心通明</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="n">
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.five_phase_burst</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>五行轮爆</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>zhuji</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>attack, spell, area, wave_clear</t>
+        </is>
+      </c>
+      <c r="H10" s="33" t="n"/>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>五行轮爆</t>
+        </is>
+      </c>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L10" s="41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O10" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="P10" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.seal_bind</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>镇灵封印</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>zhuji</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>talisman, control, seal</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="n"/>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>镇灵封印</t>
+        </is>
+      </c>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K11" s="33" t="inlineStr">
+        <is>
+          <t>max_hp</t>
+        </is>
+      </c>
+      <c r="L11" s="41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M11" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="N11" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O11" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="P11" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.thunder_judgment</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>九霄雷击</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>jindan</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>spell, thunder</t>
+        </is>
+      </c>
+      <c r="H12" s="33" t="n"/>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>九霄雷击</t>
+        </is>
+      </c>
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K12" s="33" t="inlineStr">
+        <is>
+          <t>fastest</t>
+        </is>
+      </c>
+      <c r="L12" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="N12" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O12" s="40" t="n">
+        <v>45</v>
+      </c>
+      <c r="P12" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.sword_array</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>七星剑阵</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>jindan</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>sword, formation, area</t>
+        </is>
+      </c>
+      <c r="H13" s="33" t="n"/>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>七星剑阵</t>
+        </is>
+      </c>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K13" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L13" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="N13" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O13" s="40" t="n">
+        <v>65</v>
+      </c>
+      <c r="P13" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q13" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.soul_shock</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>撼魂钟鸣</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>jindan</t>
+        </is>
+      </c>
+      <c r="G14" s="33" t="inlineStr">
+        <is>
+          <t>spirit, area</t>
+        </is>
+      </c>
+      <c r="H14" s="33" t="n"/>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>撼魂钟鸣</t>
+        </is>
+      </c>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K14" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L14" s="41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M14" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="N14" s="33" t="inlineStr">
+        <is>
+          <t>spirit</t>
+        </is>
+      </c>
+      <c r="O14" s="40" t="n">
+        <v>40</v>
+      </c>
+      <c r="P14" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.dharma_palm</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>法相镇岳掌</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>huashen</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>body, area</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="n"/>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>法相镇岳掌</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K15" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L15" s="41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="N15" s="33" t="inlineStr">
+        <is>
+          <t>stamina</t>
+        </is>
+      </c>
+      <c r="O15" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="H6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>[["attrschange","castspd","20"]]</t>
-        </is>
-      </c>
-      <c r="K6" s="21" t="inlineStr">
-        <is>
-          <t>攻击前增加20出手速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0003</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0003</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>固魂守一</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="n">
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.dream_prison</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>梦狱</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>huashen</t>
+        </is>
+      </c>
+      <c r="G16" s="33" t="inlineStr">
+        <is>
+          <t>spirit, control</t>
+        </is>
+      </c>
+      <c r="H16" s="33" t="n"/>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>梦狱</t>
+        </is>
+      </c>
+      <c r="J16" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K16" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L16" s="41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M16" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="N16" s="33" t="inlineStr">
+        <is>
+          <t>spirit</t>
+        </is>
+      </c>
+      <c r="O16" s="40" t="n">
+        <v>85</v>
+      </c>
+      <c r="P16" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.void_slash</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>斩虚</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>lianxu</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>sword, void</t>
+        </is>
+      </c>
+      <c r="H17" s="33" t="n"/>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>斩虚</t>
+        </is>
+      </c>
+      <c r="J17" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L17" s="41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M17" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O17" s="40" t="n">
+        <v>150</v>
+      </c>
+      <c r="P17" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.true_name_curse</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>真名蚀魂咒</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>lianxu</t>
+        </is>
+      </c>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>curse, spirit</t>
+        </is>
+      </c>
+      <c r="H18" s="33" t="n"/>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>真名蚀魂咒</t>
+        </is>
+      </c>
+      <c r="J18" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L18" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="N18" s="33" t="inlineStr">
+        <is>
+          <t>spirit</t>
+        </is>
+      </c>
+      <c r="O18" s="40" t="n">
+        <v>130</v>
+      </c>
+      <c r="P18" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.law_command</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>律令·止</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>heti</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>law, control, area</t>
+        </is>
+      </c>
+      <c r="H19" s="33" t="n"/>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>律令·止</t>
+        </is>
+      </c>
+      <c r="J19" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L19" s="41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M19" s="40" t="n">
+        <v>45</v>
+      </c>
+      <c r="N19" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O19" s="40" t="n">
+        <v>240</v>
+      </c>
+      <c r="P19" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.open_heaven</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>开天一式</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>dujie</t>
+        </is>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>sword, law, ultimate</t>
+        </is>
+      </c>
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="33" t="inlineStr">
+        <is>
+          <t>开天一式</t>
+        </is>
+      </c>
+      <c r="J20" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L20" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" s="40" t="n">
+        <v>120</v>
+      </c>
+      <c r="N20" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O20" s="40" t="n">
+        <v>500</v>
+      </c>
+      <c r="P20" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.cataclysm</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>劫灭神通</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>dujie</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
+        <is>
+          <t>spell, tribulation, ultimate</t>
+        </is>
+      </c>
+      <c r="H21" s="33" t="n"/>
+      <c r="I21" s="33" t="inlineStr">
+        <is>
+          <t>劫灭神通</t>
+        </is>
+      </c>
+      <c r="J21" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K21" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L21" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" s="40" t="n">
+        <v>150</v>
+      </c>
+      <c r="N21" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O21" s="40" t="n">
+        <v>550</v>
+      </c>
+      <c r="P21" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q21" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.nascent_blade</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>元婴御灵斩</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>yuanying</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>sword, spirit, ranged</t>
+        </is>
+      </c>
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>元婴御灵斩</t>
+        </is>
+      </c>
+      <c r="J22" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K22" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L22" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="N22" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O22" s="40" t="n">
+        <v>80</v>
+      </c>
+      <c r="P22" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.soul_contract_command</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>魂契敕令</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D23" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>yuanying</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>talisman, command</t>
+        </is>
+      </c>
+      <c r="H23" s="33" t="n"/>
+      <c r="I23" s="33" t="inlineStr">
+        <is>
+          <t>魂契敕令</t>
+        </is>
+      </c>
+      <c r="J23" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K23" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L23" s="41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M23" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="N23" s="33" t="inlineStr">
+        <is>
+          <t>spirit</t>
+        </is>
+      </c>
+      <c r="O23" s="40" t="n">
+        <v>70</v>
+      </c>
+      <c r="P23" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="27" customHeight="1">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.dao_sword_river</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>道剑长河</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>dacheng</t>
+        </is>
+      </c>
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>sword, law, area</t>
+        </is>
+      </c>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="33" t="inlineStr">
+        <is>
+          <t>道剑长河</t>
+        </is>
+      </c>
+      <c r="J24" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K24" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L24" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="M24" s="40" t="n">
+        <v>65</v>
+      </c>
+      <c r="N24" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O24" s="40" t="n">
+        <v>340</v>
+      </c>
+      <c r="P24" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="33" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="H7" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>get</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>[["attrschange","castspd","20"]]</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>增加20出手速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0004</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0004</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>滴血不灭</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="n">
+    </row>
+    <row r="25" ht="27" customHeight="1">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>ability.combat.world_suppression</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>掌中天地·镇</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>combat_active</t>
+        </is>
+      </c>
+      <c r="D25" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>dacheng</t>
+        </is>
+      </c>
+      <c r="G25" s="33" t="inlineStr">
+        <is>
+          <t>world, control, area</t>
+        </is>
+      </c>
+      <c r="H25" s="33" t="n"/>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>掌中天地·镇</t>
+        </is>
+      </c>
+      <c r="J25" s="33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="K25" s="33" t="inlineStr">
+        <is>
+          <t>lowest_hp</t>
+        </is>
+      </c>
+      <c r="L25" s="41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M25" s="40" t="n">
+        <v>80</v>
+      </c>
+      <c r="N25" s="33" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="O25" s="40" t="n">
+        <v>380</v>
+      </c>
+      <c r="P25" s="33" t="inlineStr">
+        <is>
+          <t>cast</t>
+        </is>
+      </c>
+      <c r="Q25" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="33" t="inlineStr">
         <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>ondie</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t>[["heal_hp","10"]]</t>
-        </is>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>死亡前回血(模拟濒死复活)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0005</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0005</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>人兵相契</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>beattacked</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>[["attrschange","castspd","20"]]</t>
-        </is>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>被攻击后增加20出手速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0006</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>fpassive_0006</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>不坏道心</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>attacked</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t>[["attrschange","castspd","20"]]</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>攻击后增加20出手速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>fpassive_0007</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>fpassive_0007</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>万劫不坏</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>get</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>[["attrschange","castspd","20"]]</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>增加20出手速度</t>
         </is>
       </c>
     </row>
@@ -1153,1954 +2579,533 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="16.25" customWidth="1" style="17" min="1" max="1"/>
-    <col width="18.75" customWidth="1" style="17" min="2" max="7"/>
-    <col width="32.5" customWidth="1" style="17" min="8" max="8"/>
-    <col width="18.75" customWidth="1" style="17" min="9" max="19"/>
-    <col width="32.5" customWidth="1" style="17" min="20" max="20"/>
-    <col width="9" customWidth="1" style="17" min="21" max="16384"/>
+    <col width="16.25" customWidth="1" style="11" min="1" max="1"/>
+    <col width="18.75" customWidth="1" style="11" min="2" max="6"/>
+    <col width="32.5" customWidth="1" style="11" min="7" max="7"/>
+    <col width="18.75" customWidth="1" style="11" min="8" max="9"/>
+    <col width="32.5" customWidth="1" style="11" min="10" max="10"/>
+    <col width="18.75" customWidth="1" style="11" min="11" max="11"/>
+    <col width="9" customWidth="1" style="11" min="12" max="12"/>
+    <col width="9" customWidth="1" style="11" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>键</t>
         </is>
       </c>
-      <c r="B1" s="30" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="30" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="30" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="E1" s="31" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>阶位</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>品质</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>req_realm</t>
-        </is>
-      </c>
-      <c r="H1" s="30" t="inlineStr">
-        <is>
-          <t>标签</t>
-        </is>
-      </c>
-      <c r="I1" s="30" t="inlineStr">
-        <is>
-          <t>vfx_preset</t>
-        </is>
-      </c>
-      <c r="J1" s="30" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>cd</t>
+        </is>
+      </c>
+      <c r="I1" s="24" t="inlineStr">
+        <is>
+          <t>runtype</t>
+        </is>
+      </c>
+      <c r="J1" s="24" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="K1" s="30" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="L1" s="30" t="inlineStr">
-        <is>
-          <t>targetarg</t>
-        </is>
-      </c>
-      <c r="M1" s="32" t="inlineStr">
-        <is>
-          <t>cast_time</t>
-        </is>
-      </c>
-      <c r="N1" s="31" t="inlineStr">
-        <is>
-          <t>cooldown</t>
-        </is>
-      </c>
-      <c r="O1" s="30" t="inlineStr">
-        <is>
-          <t>cost_resource</t>
-        </is>
-      </c>
-      <c r="P1" s="31" t="inlineStr">
-        <is>
-          <t>cost_value</t>
-        </is>
-      </c>
-      <c r="Q1" s="30" t="inlineStr">
-        <is>
-          <t>activation</t>
-        </is>
-      </c>
-      <c r="R1" s="31" t="inlineStr">
-        <is>
-          <t>power_scale</t>
-        </is>
-      </c>
-      <c r="S1" s="30" t="inlineStr">
-        <is>
-          <t>效果</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>quality</t>
         </is>
       </c>
-      <c r="G2" s="27" t="inlineStr">
-        <is>
-          <t>req_realm</t>
-        </is>
-      </c>
-      <c r="H2" s="27" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I2" s="27" t="inlineStr">
-        <is>
-          <t>vfx_preset</t>
-        </is>
-      </c>
-      <c r="J2" s="27" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="K2" s="27" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="L2" s="27" t="inlineStr">
-        <is>
-          <t>targetarg</t>
-        </is>
-      </c>
-      <c r="M2" s="29" t="inlineStr">
-        <is>
-          <t>cast_time</t>
-        </is>
-      </c>
-      <c r="N2" s="28" t="inlineStr">
-        <is>
-          <t>cooldown</t>
-        </is>
-      </c>
-      <c r="O2" s="27" t="inlineStr">
-        <is>
-          <t>cost_resource</t>
-        </is>
-      </c>
-      <c r="P2" s="28" t="inlineStr">
-        <is>
-          <t>cost_value</t>
-        </is>
-      </c>
-      <c r="Q2" s="27" t="inlineStr">
-        <is>
-          <t>activation</t>
-        </is>
-      </c>
-      <c r="R2" s="28" t="inlineStr">
-        <is>
-          <t>power_scale</t>
-        </is>
-      </c>
-      <c r="S2" s="27" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>cd</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>runtype</t>
+        </is>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>effects</t>
         </is>
       </c>
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>json</t>
+        </is>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="M3" s="26" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N3" s="25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="O3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P3" s="25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Q3" s="24" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="R3" s="25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="S3" s="24" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>k1</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
-      <c r="I4" s="24" t="n"/>
-      <c r="J4" s="24" t="n"/>
-      <c r="K4" s="24" t="n"/>
-      <c r="L4" s="24" t="n"/>
-      <c r="M4" s="26" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="24" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="24" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="24" t="n"/>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.qi_bolt</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.qi_bolt</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>御气弹</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E5" s="25" t="n">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0001</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0001</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>铁骨</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="E5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="24" t="inlineStr">
-        <is>
-          <t>qi</t>
-        </is>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>attack, spell, ranged, filler</t>
-        </is>
-      </c>
-      <c r="I5" s="24" t="inlineStr">
-        <is>
-          <t>qi_bolt_projectile</t>
-        </is>
-      </c>
-      <c r="J5" s="24" t="inlineStr">
-        <is>
-          <t>低耗灵力弹，适合新手稳定补伤害。</t>
-        </is>
-      </c>
-      <c r="K5" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L5" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M5" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N5" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P5" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R5" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="24" t="inlineStr">
-        <is>
-          <t>[["damage", "1"]]</t>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>beattack</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>[["attrschange","castspd","20"]]</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>被攻击前增加20出手速度</t>
         </is>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.wind_step</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.wind_step</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>流风步</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
-        <is>
-          <t>qi</t>
-        </is>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>mobility, shield, defense</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="inlineStr">
-        <is>
-          <t>短暂借风护身，提升出手速度并获得灵力护盾。</t>
-        </is>
-      </c>
-      <c r="K6" s="24" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
-      </c>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P6" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q6" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="24" t="inlineStr">
-        <is>
-          <t>[["buff", "buff_0001"], ["buff", "buff_0002"], ["buff", "buff_0003"], ["buff", "buff_0004"], ["buff", "buff_0005"], ["buff", "buff_0006"], ["buff", "buff_0007"]]</t>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0002</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0002</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>剑心通明</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>[["attrschange","castspd","20"]]</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>攻击前增加20出手速度</t>
         </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.sword_qi</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.sword_qi</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>破空剑气</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>qi</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>attack, sword, ranged, execute</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>sword_qi_projectile</t>
-        </is>
-      </c>
-      <c r="J7" s="24" t="inlineStr">
-        <is>
-          <t>集中剑气斩向虚弱敌人，负责收割和压低战斗时长。</t>
-        </is>
-      </c>
-      <c r="K7" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L7" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M7" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P7" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q7" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="24" t="inlineStr">
-        <is>
-          <t>[["buff", "buff_0008"], ["buff", "buff_0009"], ["buff", "buff_0010"], ["buff", "buff_0011"], ["buff", "buff_0012"], ["buff", "buff_0013"], ["buff", "buff_0014"]]</t>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0003</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0003</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>固魂守一</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>[["attrschange","castspd","20"]]</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>增加20出手速度</t>
         </is>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.blood_strike</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.blood_strike</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>震血拳</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>foundation</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>attack, body, melee, control</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="inlineStr">
-        <is>
-          <t>震血拳</t>
-        </is>
-      </c>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L8" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M8" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N8" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="O8" s="24" t="inlineStr">
-        <is>
-          <t>stamina</t>
-        </is>
-      </c>
-      <c r="P8" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q8" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R8" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="24" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0004</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0004</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>滴血不灭</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="H8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>ondie</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>[["heal_hp","10"]]</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>死亡前回血(模拟濒死复活)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.five_phase_burst</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.five_phase_burst</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>五行轮爆</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>foundation</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>attack, spell, area, wave_clear</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="24" t="inlineStr">
-        <is>
-          <t>五行轮爆</t>
-        </is>
-      </c>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L9" s="24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="M9" s="26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P9" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q9" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R9" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="24" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0005</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0005</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>人兵相契</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="H9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>beattacked</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>[["attrschange","castspd","20"]]</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>被攻击后增加20出手速度</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.seal_bind</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.seal_bind</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>镇灵封印</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>foundation</t>
-        </is>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>talisman, control, seal</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="24" t="inlineStr">
-        <is>
-          <t>镇灵封印</t>
-        </is>
-      </c>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>max_hp</t>
-        </is>
-      </c>
-      <c r="M10" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N10" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="O10" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P10" s="25" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R10" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="24" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0006</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>fpassive_0006</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>不坏道心</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="H10" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>attacked</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>[["attrschange","castspd","20"]]</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>攻击后增加20出手速度</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.thunder_judgment</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.thunder_judgment</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>九霄雷击</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>spell, thunder</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="24" t="inlineStr">
-        <is>
-          <t>九霄雷击</t>
-        </is>
-      </c>
-      <c r="K11" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L11" s="24" t="inlineStr">
-        <is>
-          <t>fastest</t>
-        </is>
-      </c>
-      <c r="M11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="O11" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P11" s="25" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q11" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R11" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="24" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>fpassive_0007</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>fpassive_0007</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>万劫不坏</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.sword_array</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.sword_array</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>七星剑阵</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>sword, formation, area</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="24" t="inlineStr">
-        <is>
-          <t>七星剑阵</t>
-        </is>
-      </c>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M12" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="25" t="n">
-        <v>24</v>
-      </c>
-      <c r="O12" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P12" s="25" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q12" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R12" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.soul_shock</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.soul_shock</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>撼魂钟鸣</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>spirit, area</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="24" t="inlineStr">
-        <is>
-          <t>撼魂钟鸣</t>
-        </is>
-      </c>
-      <c r="K13" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L13" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N13" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="O13" s="24" t="inlineStr">
-        <is>
-          <t>spirit</t>
-        </is>
-      </c>
-      <c r="P13" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R13" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.dharma_palm</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.dharma_palm</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>法相镇岳掌</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
+      <c r="H11" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>transform</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>body, area</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="24" t="inlineStr">
-        <is>
-          <t>法相镇岳掌</t>
-        </is>
-      </c>
-      <c r="K14" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M14" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N14" s="25" t="n">
-        <v>22</v>
-      </c>
-      <c r="O14" s="24" t="inlineStr">
-        <is>
-          <t>stamina</t>
-        </is>
-      </c>
-      <c r="P14" s="25" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R14" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.dream_prison</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.dream_prison</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>梦狱</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>transform</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>spirit, control</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="n"/>
-      <c r="J15" s="24" t="inlineStr">
-        <is>
-          <t>梦狱</t>
-        </is>
-      </c>
-      <c r="K15" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L15" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M15" s="26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N15" s="25" t="n">
-        <v>26</v>
-      </c>
-      <c r="O15" s="24" t="inlineStr">
-        <is>
-          <t>spirit</t>
-        </is>
-      </c>
-      <c r="P15" s="25" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q15" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R15" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.void_slash</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.void_slash</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>斩虚</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>void</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>sword, void</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="n"/>
-      <c r="J16" s="24" t="inlineStr">
-        <is>
-          <t>斩虚</t>
-        </is>
-      </c>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M16" s="26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N16" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="O16" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P16" s="25" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q16" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.true_name_curse</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.true_name_curse</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>真名蚀魂咒</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>void</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>curse, spirit</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="n"/>
-      <c r="J17" s="24" t="inlineStr">
-        <is>
-          <t>真名蚀魂咒</t>
-        </is>
-      </c>
-      <c r="K17" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L17" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M17" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="25" t="n">
-        <v>25</v>
-      </c>
-      <c r="O17" s="24" t="inlineStr">
-        <is>
-          <t>spirit</t>
-        </is>
-      </c>
-      <c r="P17" s="25" t="n">
-        <v>130</v>
-      </c>
-      <c r="Q17" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R17" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.law_command</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.law_command</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>律令·止</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>merge</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>law, control, area</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="n"/>
-      <c r="J18" s="24" t="inlineStr">
-        <is>
-          <t>律令·止</t>
-        </is>
-      </c>
-      <c r="K18" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M18" s="26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N18" s="25" t="n">
-        <v>45</v>
-      </c>
-      <c r="O18" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P18" s="25" t="n">
-        <v>240</v>
-      </c>
-      <c r="Q18" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.open_heaven</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.open_heaven</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>开天一式</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>tribulation</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>sword, law, ultimate</t>
-        </is>
-      </c>
-      <c r="I19" s="24" t="n"/>
-      <c r="J19" s="24" t="inlineStr">
-        <is>
-          <t>开天一式</t>
-        </is>
-      </c>
-      <c r="K19" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L19" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M19" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N19" s="25" t="n">
-        <v>120</v>
-      </c>
-      <c r="O19" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P19" s="25" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q19" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R19" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.cataclysm</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.cataclysm</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>劫灭神通</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>tribulation</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>spell, tribulation, ultimate</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="n"/>
-      <c r="J20" s="24" t="inlineStr">
-        <is>
-          <t>劫灭神通</t>
-        </is>
-      </c>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M20" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" s="25" t="n">
-        <v>150</v>
-      </c>
-      <c r="O20" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P20" s="25" t="n">
-        <v>550</v>
-      </c>
-      <c r="Q20" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R20" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.nascent_blade</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.nascent_blade</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>元婴御灵斩</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
-        <is>
-          <t>nascent</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>sword, spirit, ranged</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="n"/>
-      <c r="J21" s="24" t="inlineStr">
-        <is>
-          <t>元婴御灵斩</t>
-        </is>
-      </c>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L21" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="O21" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P21" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q21" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R21" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.soul_contract_command</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.soul_contract_command</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>魂契敕令</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>nascent</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>talisman, command</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="n"/>
-      <c r="J22" s="24" t="inlineStr">
-        <is>
-          <t>魂契敕令</t>
-        </is>
-      </c>
-      <c r="K22" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L22" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M22" s="26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <v>18</v>
-      </c>
-      <c r="O22" s="24" t="inlineStr">
-        <is>
-          <t>spirit</t>
-        </is>
-      </c>
-      <c r="P22" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q22" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.dao_sword_river</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.dao_sword_river</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>道剑长河</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
-        <is>
-          <t>great</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>sword, law, area</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="n"/>
-      <c r="J23" s="24" t="inlineStr">
-        <is>
-          <t>道剑长河</t>
-        </is>
-      </c>
-      <c r="K23" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L23" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M23" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>65</v>
-      </c>
-      <c r="O23" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P23" s="25" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q23" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R23" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.world_suppression</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>ability.combat.world_suppression</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>掌中天地·镇</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>combat_active</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>great</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>world, control, area</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="n"/>
-      <c r="J24" s="24" t="inlineStr">
-        <is>
-          <t>掌中天地·镇</t>
-        </is>
-      </c>
-      <c r="K24" s="24" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>lowest_hp</t>
-        </is>
-      </c>
-      <c r="M24" s="26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N24" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="O24" s="24" t="inlineStr">
-        <is>
-          <t>mana</t>
-        </is>
-      </c>
-      <c r="P24" s="25" t="n">
-        <v>380</v>
-      </c>
-      <c r="Q24" s="24" t="inlineStr">
-        <is>
-          <t>cast</t>
-        </is>
-      </c>
-      <c r="R24" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" s="24" t="inlineStr">
-        <is>
-          <t>[]</t>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>[["attrschange","castspd","20"]]</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>增加20出手速度</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3130,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>键</t>
         </is>
@@ -3622,7 +3627,7 @@
       </c>
       <c r="X5" s="7" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3733,7 @@
       </c>
       <c r="X6" s="7" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3839,7 @@
       </c>
       <c r="X7" s="7" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3945,7 @@
       </c>
       <c r="X8" s="7" t="inlineStr">
         <is>
-          <t>qi</t>
+          <t>lianqi</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4051,7 @@
       </c>
       <c r="X9" s="7" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4157,7 @@
       </c>
       <c r="X10" s="7" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4263,7 @@
       </c>
       <c r="X11" s="7" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4369,7 @@
       </c>
       <c r="X12" s="7" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4475,7 @@
       </c>
       <c r="X13" s="7" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>zhuji</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4581,7 @@
       </c>
       <c r="X14" s="7" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>jindan</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4687,7 @@
       </c>
       <c r="X15" s="7" t="inlineStr">
         <is>
-          <t>void</t>
+          <t>lianxu</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4793,7 @@
       </c>
       <c r="X16" s="7" t="inlineStr">
         <is>
-          <t>merge</t>
+          <t>heti</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4899,7 @@
       </c>
       <c r="X17" s="7" t="inlineStr">
         <is>
-          <t>tribulation</t>
+          <t>dujie</t>
         </is>
       </c>
     </row>
@@ -4912,909 +4917,910 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="16.25" customWidth="1" style="17" min="1" max="1"/>
-    <col width="18.75" customWidth="1" style="17" min="2" max="9"/>
-    <col width="32.5" customWidth="1" style="17" min="10" max="11"/>
-    <col width="9" customWidth="1" style="17" min="12" max="16384"/>
+    <col width="16.25" customWidth="1" style="11" min="1" max="1"/>
+    <col width="18.75" customWidth="1" style="11" min="2" max="9"/>
+    <col width="32.5" customWidth="1" style="11" min="10" max="11"/>
+    <col width="9" customWidth="1" style="11" min="12" max="12"/>
+    <col width="9" customWidth="1" style="11" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>键</t>
         </is>
       </c>
-      <c r="B1" s="30" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="30" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="30" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>图标</t>
         </is>
       </c>
-      <c r="E1" s="30" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="F1" s="30" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>max_stacks</t>
         </is>
       </c>
-      <c r="I1" s="32" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>ticktime</t>
         </is>
       </c>
-      <c r="J1" s="30" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>modifiers</t>
         </is>
       </c>
-      <c r="K1" s="30" t="inlineStr">
+      <c r="K1" s="24" t="inlineStr">
         <is>
           <t>tick_effects</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="F2" s="27" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>max_stacks</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t>ticktime</t>
         </is>
       </c>
-      <c r="J2" s="27" t="inlineStr">
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>modifiers</t>
         </is>
       </c>
-      <c r="K2" s="27" t="inlineStr">
+      <c r="K2" s="21" t="inlineStr">
         <is>
           <t>tick_effects</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G3" s="25" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>json</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>json</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>k1</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="26" t="n"/>
-      <c r="J4" s="24" t="n"/>
-      <c r="K4" s="24" t="n"/>
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="20" t="n"/>
+      <c r="J4" s="18" t="n"/>
+      <c r="K4" s="18" t="n"/>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>buff_0001</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>buff_0001</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>流风护身</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>身形随风而动，短时间提高出手速度。</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="23" t="n">
+      <c r="I5" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>[["attrschange","castspd","20"]]</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>buff_0002</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>buff_0002</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>五行易伤</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>ui_new/huo.png</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>五行气机失衡，受到伤害提高。</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>buff_0003</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>buff_0003</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>神识压制</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>神识受制，控制抗性降低。</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="23" t="n">
+      <c r="I7" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>buff_0004</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>buff_0004</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>抗性崩解</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>护体灵机破散，受到伤害提高。</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>buff_0005</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>buff_0005</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>劫痕</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>ui_new/huo.png</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>劫力留痕，受到伤害提高。</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I9" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>buff_0006</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>buff_0006</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>疗愈阻断</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>生机流转受阻，生命恢复降低。</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="23" t="n">
+      <c r="I10" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>buff_0007</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>buff_0007</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>踉跄</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>身形不稳，行动速度大幅降低。</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>debuff,control</t>
         </is>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>buff_0008</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>buff_0008</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>封印</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>灵机被封，行动速度大幅降低。</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>debuff,control</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K12" s="21" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>buff_0009</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>buff_0009</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>麻痹</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>经脉麻痹，行动速度大幅降低。</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>debuff,control</t>
         </is>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>buff_0010</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>buff_0010</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>打断</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>施法被扰，行动速度大幅降低。</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>debuff,control</t>
         </is>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="23" t="n">
+      <c r="I14" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K14" s="21" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>buff_0011</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>buff_0011</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>击倒</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>被击倒在地，行动速度大幅降低。</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>debuff,control</t>
         </is>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K15" s="21" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>buff_0012</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>buff_0012</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>律令压制</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>受律令镇压，行动速度大幅降低。</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>debuff,control</t>
         </is>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K16" s="21" t="inlineStr">
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>buff_0013</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>buff_0013</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>迟缓</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>ui_new/skill_03.png</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>神识受扰，出手速度降低。</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I17" s="17" t="n">
         <v>-1</v>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>[["attrschange","castspd","-20"]]</t>
         </is>
       </c>
-      <c r="K17" s="21" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>buff_0014</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>buff_0014</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>灼烧</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>ui_new/huo.png</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>灵毒灼烧经脉，周期损失气血。</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="20" t="n">
+      <c r="I18" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>[["damage","10","atk","100"]]</t>
         </is>
@@ -5831,381 +5837,515 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="16.25" customWidth="1" style="17" min="1" max="1"/>
-    <col width="18.75" customWidth="1" style="17" min="2" max="8"/>
-    <col width="9" customWidth="1" style="17" min="9" max="16384"/>
+    <col width="16.25" customWidth="1" style="11" min="1" max="1"/>
+    <col width="18.75" customWidth="1" style="11" min="2" max="8"/>
+    <col width="9" customWidth="1" style="11" min="9" max="9"/>
+    <col width="9" customWidth="1" style="11" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>键</t>
         </is>
       </c>
-      <c r="B1" s="30" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>效果ID</t>
         </is>
       </c>
-      <c r="C1" s="30" t="inlineStr">
+      <c r="C1" s="31" t="inlineStr">
         <is>
           <t>中文介绍</t>
         </is>
       </c>
-      <c r="D1" s="30" t="inlineStr">
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="E1" s="30" t="inlineStr">
+      <c r="E1" s="31" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="F1" s="30" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>参数3</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>参数4</t>
         </is>
       </c>
-      <c r="H1" s="30" t="inlineStr">
+      <c r="H1" s="31" t="inlineStr">
         <is>
           <t>参数5</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>效果ID</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>中文介绍</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>参数1</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>参数2</t>
         </is>
       </c>
-      <c r="F2" s="27" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>参数3</t>
         </is>
       </c>
-      <c r="G2" s="27" t="inlineStr">
+      <c r="G2" s="32" t="inlineStr">
         <is>
           <t>参数4</t>
         </is>
       </c>
-      <c r="H2" s="27" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>参数5</t>
         </is>
       </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>属性</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="33" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>战斗属性键</t>
+        </is>
+      </c>
+      <c r="L3" s="28" t="inlineStr">
+        <is>
+          <t>含义</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>k1</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="24" t="n"/>
-      <c r="G4" s="24" t="n"/>
-      <c r="H4" s="24" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>spd</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>出手速度</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>damage</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>自身属性类型</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>自身属性百分比(1000 = 100%)(跟据属性类型对应属性值计算加成)</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t>目标属性</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="34" t="inlineStr">
         <is>
           <t>目标属性百分比(1000 = 100%)(跟据目标属性类型对应属性值计算加成)</t>
         </is>
       </c>
+      <c r="K5" s="29" t="inlineStr">
+        <is>
+          <t>physical_atk</t>
+        </is>
+      </c>
+      <c r="L5" s="30" t="inlineStr">
+        <is>
+          <t>物理攻击</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>护盾</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>自身属性类型</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>自身属性百分比(1000 = 100%)(跟据属性类型对应属性值计算加成)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>目标属性</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>目标属性百分比(1000 = 100%)(跟据目标属性类型对应属性值计算加成)</t>
         </is>
       </c>
+      <c r="K6" s="29" t="inlineStr">
+        <is>
+          <t>magic_atk</t>
+        </is>
+      </c>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>法术攻击</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>heal_hp</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>heal_hp</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>回血</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="34" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>自身属性类型</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>自身属性百分比(1000 = 100%)(跟据属性类型对应属性值计算加成)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>目标属性</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="34" t="inlineStr">
         <is>
           <t>目标属性百分比(1000 = 100%)(跟据目标属性类型对应属性值计算加成)</t>
         </is>
       </c>
+      <c r="K7" s="29" t="inlineStr">
+        <is>
+          <t>physical_def</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>物理防御</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>restore_mana</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>restore_mana</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>回蓝</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>自身属性类型</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>自身属性百分比(1000 = 100%)(跟据属性类型对应属性值计算加成)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>目标属性</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="34" t="inlineStr">
         <is>
           <t>目标属性百分比(1000 = 100%)(跟据目标属性类型对应属性值计算加成)</t>
         </is>
       </c>
+      <c r="K8" s="29" t="inlineStr">
+        <is>
+          <t>magic_def</t>
+        </is>
+      </c>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>法术防御</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>attrschange</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>attrschange</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>战斗属性改变</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="34" t="inlineStr">
         <is>
           <t>属性类型</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>固定修改值</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="34" t="inlineStr">
         <is>
           <t>百分比修改值</t>
         </is>
       </c>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="K9" s="29" t="inlineStr">
+        <is>
+          <t>hp_max</t>
+        </is>
+      </c>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>生命上限</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>buff</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>持续效果</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>buffid</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="K10" s="29" t="inlineStr">
+        <is>
+          <t>mp_max</t>
+        </is>
+      </c>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>灵力上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="K11" s="29" t="inlineStr">
+        <is>
+          <t>hp_regen</t>
+        </is>
+      </c>
+      <c r="L11" s="30" t="inlineStr">
+        <is>
+          <t>生命回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="K12" s="29" t="inlineStr">
+        <is>
+          <t>mp_regen</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>灵力回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25.5" customHeight="1">
+      <c r="K13" s="29" t="inlineStr">
+        <is>
+          <t>damage_bonus</t>
+        </is>
+      </c>
+      <c r="L13" s="30" t="inlineStr">
+        <is>
+          <t>伤害加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="K14" s="29" t="inlineStr">
+        <is>
+          <t>control_resist</t>
+        </is>
+      </c>
+      <c r="L14" s="30" t="inlineStr">
+        <is>
+          <t>控制抗性</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
